--- a/files/港岛-赤柱-One Stanley.xlsx
+++ b/files/港岛-赤柱-One Stanley.xlsx
@@ -735,7 +735,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -868,11 +868,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K3" s="5" t="n">
-        <v>83071200</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>32564</v>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -903,7 +907,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -930,11 +934,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="5" t="n">
-        <v>86200000</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>35155</v>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -965,7 +973,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -976,7 +984,11 @@
           <t>已售</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="n">
         <v>173614212</v>
       </c>
@@ -988,11 +1000,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>173614212</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>70403</v>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -1023,7 +1039,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -1034,7 +1050,11 @@
           <t>已售</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
       <c r="H6" s="5" t="n">
         <v>173614212</v>
       </c>
@@ -1046,11 +1066,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>173614212</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>70403</v>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1081,7 +1105,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -1108,11 +1132,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="5" t="n">
-        <v>85020000</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>34887</v>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1143,7 +1171,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -1170,11 +1198,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>94685400</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>36900</v>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1237,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1216,7 +1248,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -1271,7 +1307,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -1298,11 +1334,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
-        <v>84118889</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>34111</v>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1333,7 +1373,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -1360,11 +1400,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>119800000</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>37298</v>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1395,7 +1439,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1422,11 +1466,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="5" t="n">
-        <v>127760000</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>39950</v>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1457,7 +1505,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1484,11 +1532,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>73370000</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>39638</v>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1519,7 +1571,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1546,11 +1598,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>63727200</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>33002</v>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1581,7 +1637,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1608,11 +1664,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>53150350</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>29446</v>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1643,7 +1703,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1670,11 +1730,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K16" s="5" t="n">
-        <v>53870000</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>29502</v>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1705,7 +1769,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1732,11 +1796,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>61088000</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>33003</v>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1767,7 +1835,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1794,11 +1862,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K18" s="5" t="n">
-        <v>60830700</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>31502</v>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1829,7 +1901,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1856,11 +1928,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K19" s="5" t="n">
-        <v>55330000</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>30654</v>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1967,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1918,11 +1994,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>52540000</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>28773</v>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1953,7 +2033,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -1980,11 +2060,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="5" t="n">
-        <v>67516975</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>36086</v>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2015,7 +2099,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -2026,7 +2110,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -2081,7 +2169,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -2092,7 +2180,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -2158,7 +2250,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -2224,7 +2320,11 @@
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -2279,7 +2379,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -2306,11 +2406,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>77078792</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>41197</v>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2445,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -2352,7 +2456,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -2407,7 +2515,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -2418,7 +2526,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -2500,11 +2612,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>29376</v>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2546,7 +2662,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -2628,11 +2748,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n">
-        <v>43820000</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>37421</v>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2690,11 +2814,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K32" s="5" t="n">
-        <v>43804800</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>37440</v>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2725,7 +2853,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -2752,11 +2880,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n">
-        <v>68120000</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>27129</v>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2787,7 +2919,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2798,7 +2930,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -2880,11 +3016,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="5" t="n">
-        <v>31594600</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>28801</v>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2942,11 +3082,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="5" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>26000</v>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3004,11 +3148,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="5" t="n">
-        <v>43800000</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>37404</v>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3066,11 +3214,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K38" s="5" t="n">
-        <v>43804800</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>37440</v>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3101,7 +3253,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -3112,7 +3264,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -3167,7 +3323,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -3178,7 +3334,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -3244,7 +3404,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -3326,11 +3490,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K42" s="5" t="n">
-        <v>29110000</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>26464</v>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3372,7 +3540,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -3438,7 +3610,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -3493,7 +3669,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
@@ -3504,7 +3680,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -3559,7 +3739,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -3570,7 +3750,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -3652,11 +3836,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K47" s="5" t="n">
-        <v>27680000</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>25232</v>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3698,7 +3886,11 @@
           <t>待售</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
           <t>暂无</t>
@@ -3753,7 +3945,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -3780,11 +3972,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K49" s="5" t="n">
-        <v>82231500</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>33743</v>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3815,7 +4011,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -3842,11 +4038,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K50" s="5" t="n">
-        <v>87760000</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>35791</v>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3877,7 +4077,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
@@ -3904,11 +4104,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K51" s="5" t="n">
-        <v>87780000</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>36034</v>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3939,7 +4143,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>4房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -3950,7 +4154,11 @@
           <t>在售</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
           <t>招标单位</t>
@@ -6297,7 +6505,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 2403呎 (4房)
+          <t>A | 2403呎 (4+房)
 -
 -
 (待售)</t>
@@ -6305,7 +6513,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 2511呎 (4房)
+          <t>B | 2511呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -6477,7 +6685,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 2456呎 (4房)
+          <t>A | 2456呎 (4+房)
 -
 -
 (待售)</t>
@@ -6485,7 +6693,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 2565呎 (4房)
+          <t>B | 2565呎 (4+房)
 -
 -
 (待售)</t>
@@ -6648,7 +6856,7 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2452呎 (4房)
+          <t>C | 2452呎 (4+房)
 $8776万
 $35,791/呎
 (26年-06月-08日)</t>
@@ -6656,7 +6864,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2437呎 (4房)
+          <t>D | 2437呎 (4+房)
 $8223万
 $33,743/呎
 (25年-10月-07日)</t>
@@ -6671,7 +6879,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2436呎 (4房)
+          <t>A | 2436呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -6679,7 +6887,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2436呎 (4房)
+          <t>B | 2436呎 (4+房)
 $8778万
 $36,034/呎
 (25年-10月-30日)</t>
@@ -7290,7 +7498,7 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2452呎 (4房)
+          <t>C | 2452呎 (4+房)
 $8620万
 $35,155/呎
 (26年-07月-06日)</t>
@@ -7298,7 +7506,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2551呎 (4房)
+          <t>D | 2551呎 (4+房)
 $8307万
 $32,564/呎
 (24年-05月-23日)</t>
@@ -7313,18 +7521,18 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2466呎 (4房)
+          <t>A | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(已售)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2466呎 (4房)
+          <t>B | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(已售)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7463,7 +7671,7 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 2566呎 (4房)
+          <t>C | 2566呎 (4+房)
 $9469万
 $36,900/呎
 (24年-08月-04日)</t>
@@ -7471,7 +7679,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>D | 2437呎 (4房)
+          <t>D | 2437呎 (4+房)
 $8502万
 $34,887/呎
 (26年-05月-10日)</t>
@@ -7486,7 +7694,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2466呎 (4房)
+          <t>A | 2466呎 (4+房)
 $8412万
 $34,111/呎
 (24年-05月-09日)</t>
@@ -7494,7 +7702,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 2436呎 (4房)
+          <t>B | 2436呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -7623,7 +7831,7 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 3212呎 (4房)
+          <t>B | 3212呎 (4+房)
 $11980万
 $37,298/呎
 (26年-06月-07日)</t>
@@ -7638,7 +7846,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 3198呎 (4房)
+          <t>A | 3198呎 (4+房)
 $12776万
 $39,950/呎
 (26年-05月-18日)</t>
@@ -7765,7 +7973,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4房)
+          <t>A | 1931呎 (4+房)
 $6373万
 $33,002/呎
 (24年-05月-16日)</t>
@@ -7773,7 +7981,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1851呎 (4房)
+          <t>B | 1851呎 (4+房)
 $7337万
 $39,638/呎
 (26年-06月-02日)</t>
@@ -7788,7 +7996,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1826呎 (4房)
+          <t>A | 1826呎 (4+房)
 $5387万
 $29,502/呎
 (26年-03月-24日)</t>
@@ -7796,7 +8004,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 1805呎 (4房)
+          <t>B | 1805呎 (4+房)
 $5315万
 $29,446/呎
 (24年-05月-13日)</t>
@@ -7922,7 +8130,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4房)
+          <t>A | 1931呎 (4+房)
 $6083万
 $31,502/呎
 (24年-05月-13日)</t>
@@ -7930,7 +8138,7 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1851呎 (4房)
+          <t>B | 1851呎 (4+房)
 $6109万
 $33,003/呎
 (24年-05月-19日)</t>
@@ -7945,7 +8153,7 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1826呎 (4房)
+          <t>A | 1826呎 (4+房)
 $5254万
 $28,773/呎
 (25年-02月-05日)</t>
@@ -7953,7 +8161,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 1805呎 (4房)
+          <t>B | 1805呎 (4+房)
 $5533万
 $30,654/呎
 (25年-11月-24日)</t>
@@ -8079,7 +8287,7 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1871呎 (4房)
+          <t>A | 1871呎 (4+房)
 $6752万
 $36,086/呎
 (24年-11月-13日)</t>
@@ -8095,7 +8303,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 1874呎 (4房)
+          <t>A | 1874呎 (4+房)
 -
 -
 (待售)</t>
@@ -8103,7 +8311,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 1855呎 (4房)
+          <t>B | 1855呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -8253,7 +8461,7 @@
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1871呎 (4房)
+          <t>B | 1871呎 (4+房)
 $7708万
 $41,197/呎
 (25年-02月-17日)</t>
@@ -8268,7 +8476,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4房)
+          <t>A | 1931呎 (4+房)
 -
 -
 (待售)</t>
@@ -8276,7 +8484,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>B | 1910呎 (4房)
+          <t>B | 1910呎 (4+房)
 -
 -
 (待售)</t>
@@ -8448,7 +8656,7 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>A | 2403呎 (4房)
+          <t>A | 2403呎 (4+房)
 -
 -
 (待售)</t>
@@ -8456,7 +8664,7 @@
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 2511呎 (4房)
+          <t>B | 2511呎 (4+房)
 $6812万
 $27,129/呎
 (26年-05月-10日)</t>
